--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0071.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0071.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hanakage Underground Street</t>
+          <t>Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Honami Central Park</t>
+          <t>Công Viên Trung Tâm Honami</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Neon Tower</t>
+          <t>Tháp Neon</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Sakura Quarter</t>
+          <t>Khu Sakura</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Storage Bag Vật phẩm' Total Value</t>
+          <t>Tổng Giá Trị Vật Phẩm Trong Túi Lưu Trữ</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cafe Decor Bonus</t>
+          <t>Thưởng trang trí quán cà phê</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Thời gian hoàn thành</t>
+          <t>Xóa bỏ Thời Gian</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Rice Dango Income</t>
+          <t>Thu Nhập Bánh Dango Gạo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Safe Extraction</t>
+          <t>Đưa Về An Toàn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Not Now</t>
+          <t>Không phải lúc này</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Extract Now</t>
+          <t>Tách chiết ngay</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Forced Extraction</t>
+          <t>Cưỡng Chế Khai Thác</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Forced Extraction</t>
+          <t>Cưỡng Chế Khai Thác</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Sắp xếp</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Quick Sell</t>
+          <t>Bán Nhanh</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tự động trang bị</t>
+          <t>Trang bị tự động</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tháo Tất Cả</t>
+          <t>Tháo Tất Cả Trang Bị</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Bán</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trang Bị Nhanh</t>
+          <t>Trang bị nhanh</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Bán</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Discard</t>
+          <t>Hủy Bỏ</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Quick Thu thập</t>
+          <t>Thu thập nhanh</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Xóa Nhanh</t>
+          <t>Gỡ bỏ nhanh</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Phần thưởng thấp hơn vật phẩm đang trang bị</t>
+          <t>Thưởng thấp hơn vật phẩm đang trang bị</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Bạn không thể bán vật phẩm đã khóa</t>
+          <t>Bạn không thể bán vật phẩm đang khóa</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>Thay thế</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho Hàng</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Tấn Công</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Exploration</t>
+          <t>Thám Hiểm</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Survival</t>
+          <t>Sinh tồn</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Trang Bị</t>
+          <t>Trang bị</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Hủy Theo Dõi</t>
+          <t>Hủy theo dõi</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết bất thường ở Hành Lang Meishin</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nhận Huy hiệu Namipon</t>
+          <t>Nhận Huy Hiệu Namipon</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết bất thường ở Phố Ngầm Hanakage</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Nhận Huy hiệu Namipon</t>
+          <t>Nhận Huy Hiệu Namipon</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết bất thường ở Phố Ngầm Hanakage</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Mở khóa cùng với sự kiện Sự Việc Kỳ Lạ Ở Honami</t>
+          <t>Mở khóa cùng với Sự Kiện Kỳ Lạ trong sự kiện Honami</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết bất thường ở Hành Lang Meishin</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Nhận Huy hiệu Namipon</t>
+          <t>Nhận Huy Hiệu Namipon</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết bất thường ở Phố Ngầm Hanakage</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Mở khóa khi hoàn thành nhiệm vụ khám phá đầu tiên trong Sự Việc Kỳ Lạ Ở Honami</t>
+          <t>Mở khóa sau khi hoàn thành nhiệm vụ khám phá đầu tiên trong Sự Việc Kỳ Lạ Ở Honami</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi giải quyết bất thường ở Phố Ngầm Hanakage</t>
+          <t>Mở khóa sau khi giải quyết bất thường tại Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho Hàng</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Đã thả</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Vật phẩm chiến lợi phẩm này không thể trang bị</t>
+          <t>Vật phẩm chiến lợi phẩm này không thể trang bị được</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Không đủ dung lượng Túi Lưu Trữ</t>
+          <t>Túi Lưu Trữ không đủ dung lượng</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Insufficent Rice Dangos</t>
+          <t>Không đủ Bánh Gạo Dango</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Mở khóa ô Sticker mới</t>
+          <t>Ô Dán Hình Mới Được Mở Khóa</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Namipon Badge lên cấp</t>
+          <t>Nâng Cấp Huy Hiệu Namipon</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Max Stability</t>
+          <t>Độ ổn định tối đa</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Độ Ổn Định tối đa tăng lên</t>
+          <t>Độ ổn định tối đa tăng lên</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Vui lòng chọn một ô để thay thế</t>
+          <t>Hãy chọn một ô để thay thế.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Giá Trị</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Giá Trị</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đã trang bị tối ưu</t>
+          <t>Đã trang bị tối ưu rồi</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi Resonator</t>
+          <t>Không thể đổi Resonator</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi Namipon</t>
+          <t>Không thể đổi Namipons</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Explorable - Sakura Quarter</t>
+          <t>Khám Phá - Khu Phố Sakura</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Explorable - Meishin Passageway</t>
+          <t>Khám Phá - Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Unlocked - Explore Honami</t>
+          <t>Đã mở khóa - Khám phá Honami</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Explorable - Honami Central Park</t>
+          <t>Khám Phá - Công Viên Trung Tâm Honami</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Unlocked - Explore Honami</t>
+          <t>Đã mở khóa - Khám phá Honami</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Unlocked - Neon Tower</t>
+          <t>Mở khóa - Tháp Neon</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Rare, Unique, Limited</t>
+          <t>Hiếm, Độc Nhất, Giới Hạn</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Rare, Unique, Limited</t>
+          <t>Hiếm, Độc Nhất, Giới Hạn</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Rare, Unique, Limited</t>
+          <t>Hiếm, Độc Nhất, Giới Hạn</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Rare, Unique, Limited, Legendary</t>
+          <t>Hiếm, Độc Nhất, Giới Hạn, Huyền Thoại</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Explore Honami</t>
+          <t>Khám phá Honami</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Main Objectives</t>
+          <t>Nhiệm vụ chính</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Mục Tiêu Phụ</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ sự kiện để mở khóa</t>
+          <t>Hoàn thành các nhiệm vụ sự kiện để mở khóa</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>New Update Highlight</t>
+          <t>Điểm nổi bật của bản cập nhật mới</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>We Who See the Stars</t>
+          <t>Chúng Ta Là Những Kẻ Ngắm Sao</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Resonator &amp; Vũ khí mới</t>
+          <t>Resonator &amp; Vũ Khí Mới</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nhiệm vụ chính mới</t>
+          <t>Nhiệm Vụ Chính Mới</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>New Region</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Intel Briefing</t>
+          <t>Báo cáo Tình báo</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Sự kiện &amp; Lối chơi mới</t>
+          <t>Sự Kiện &amp; Chế Độ Chơi Mới</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Key Updates</t>
+          <t>Cập Nhật Chính</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Resonator &amp; Vũ khí mới</t>
+          <t>Resonator &amp; Vũ Khí Mới</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Nhiệm vụ chính mới</t>
+          <t>Nhiệm Vụ Chính Mới</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>New Region</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Intel Briefing</t>
+          <t>Báo cáo Tình báo</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Sự kiện &amp; Lối chơi mới</t>
+          <t>Sự Kiện &amp; Chế Độ Chơi Mới</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Key Updates</t>
+          <t>Cập Nhật Chính</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Starfield Calibrator</t>
+          <t>Điều Tần Sao Trời</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>New Resonators</t>
+          <t>Resonator Mới</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>New Weapons</t>
+          <t>Vũ Khí Mới</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Starfield Calibrator</t>
+          <t>Điều Tần Sao Trời</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Undefined Spectrum</t>
+          <t>Quang Phổ Vô Định</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Distant May the Starlights Be</t>
+          <t>Ánh Sao Xa Xôi</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Synth Armament: Broadblade</t>
+          <t>Vũ Khí Tổng Hợp: Đại Kiếm</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Synth Armament: Kiếm</t>
+          <t>Vũ Khí Tổng Hợp: Kiếm</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Synth Armament: Pistols</t>
+          <t>Vũ Khỉ Tổng Hợp: Súng Ngắn</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Synth Armament: Gauntlets</t>
+          <t>Vũ Khí Tổng Hợp: Găng Tay</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Synth Armament: Rectifier</t>
+          <t>Vũ Khí Tổng Hợp: Bộ Chỉnh Lưu</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Featured Resonator Triệu Tập</t>
+          <t>Triệu Hồi Resonator Đặc Sắc</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Featured Weapon Triệu Tập</t>
+          <t>Triệu Hồi Vũ Khí Đặc Sắc</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Weapon Triệu Tập</t>
+          <t>Triệu Hồi Vũ Khí Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Featured Triệu Tập</t>
+          <t>Triệu Hồi Đặc Sắc</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Có thể nhận qua</t>
+          <t>Có thể nhận thông qua</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Echo: Reactor Husk</t>
+          <t>Echo: Xác Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Sonata: Pact of Neonlight Leap</t>
+          <t>Sonata: Giao Ước Nhảy Vọt Ánh Neon</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Sonata: Halo of Starry Radiance</t>
+          <t>Sonata: Vầng Hào Quang Sao Sáng</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Sonata: Rite of Gilded Revelation</t>
+          <t>Sonata: Nghi Lễ Khải Huyền Rực Rỡ</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kẻ Địch Mới</t>
+          <t>Kẻ Thù Mới</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>New Echoes</t>
+          <t>Những Echo Mới</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>New Sonata Effects</t>
+          <t>Hiệu Ứng Sonata Mới</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nghi Lễ Khải Huyền Hoàng Kim</t>
+          <t>Rite of Gilded Revelation</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>COST 4</t>
+          <t>CHI PHÍ 4</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>COST 4</t>
+          <t>CHI PHÍ 4</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Healing+</t>
+          <t>Hồi phục+</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Sonata Effect</t>
+          <t>Hiệu Ứng Sonata</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Khúc Ca Bình Minh Thứ Hai</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Điều Gì Cháy Dưới Vùng Đất Băng Giá</t>
+          <t>Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Khúc Ca Sunrise Thứ Hai</t>
+          <t>Khúc Ca Bình Minh Thứ Hai</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Chương III Hồi I "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
+          <t>Chương III Hồi I "Lửa Cháy Dưới Lãnh Nguyên"</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory</t>
+          <t>Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Starward Riseway</t>
+          <t>Đại Lộ Sao Chổi</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Argentflare Drapes</t>
+          <t>Rèm Lửa Bạc</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory</t>
+          <t>Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Starward Riseway</t>
+          <t>Đại Lộ Sao Chổi</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Argentflare Drapes</t>
+          <t>Rèm Lửa Bạc</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>New Region</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>New Region</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>New Outfits</t>
+          <t>Trang Phục Mới</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>New Outfits</t>
+          <t>Trang Phục Mới</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Sắp ra mắt</t>
+          <t>Hãy chờ nhé.</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Lahai-Roi Pioneers</t>
+          <t>Những Tiên Phong Lahai-Roi</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bắt Ánh Sao</t>
+          <t>Ghi lại Ánh Sao</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Đến Học Viện Startorch &amp; Quà Tuần Lễ Tân Sinh Viên</t>
+          <t>Đến Học Viện Startorch &amp; Quà Tuần Lễ Tân Sinh Viên</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Đua Startorch</t>
+          <t>Đua Xe Sao Chổi</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Phi Công</t>
+          <t>Ma trận Tốt Đôi: Phi Công</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Lahai-Roi Pioneers</t>
+          <t>Những Tiên Phong Lahai-Roi</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Bắt Ánh Sao</t>
+          <t>Ghi lại Ánh Sao</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Đến Học Viện Startorch &amp; Quà Tuần Lễ Tân Sinh Viên</t>
+          <t>Đến Học Viện Startorch &amp; Quà Tuần Lễ Tân Sinh Viên</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Đua Startorch</t>
+          <t>Đua Xe Sao Chổi</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Đỉnh Danh Vọng: Trận tái đấu</t>
+          <t>Đỉnh Vinh Quang: Cuộc Đọ Sức Nảy Lửa</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Phi Công</t>
+          <t>Ma trận Tốt Đôi: Phi Công</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Featured Events</t>
+          <t>Các Sự Kiện Nổi Bật</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Off-Tune Mechanic</t>
+          <t>Cơ Chế Lệch Tần</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>WavesLine</t>
+          <t>Đường Sóng</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Databank Expansion</t>
+          <t>Mở Rộng Kho Dữ Liệu</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Xe máy Thám hiểm</t>
+          <t>Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Off-Tune Mechanic</t>
+          <t>Cơ Chế Lệch Tần</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>WavesLine</t>
+          <t>Đường Sóng</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Databank Expansion</t>
+          <t>Mở Rộng Kho Dữ Liệu</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Key Updates</t>
+          <t>Cập Nhật Chính</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Ầu, ảnh mờ quá…</t>
+          <t>Ôi, ảnh mờ hết cả rồi…</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Pioneer Training Ground</t>
+          <t>Khu Huấn Luyện Tiên Phong</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Tần số đã khôi phục</t>
+          <t>Tần số đã được khôi phục.</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Underground "Sun"</t>
+          <t>"Mặt Trời" Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Nhà Ăn Sinh Viên</t>
+          <t>Nhà ăn học sinh</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Orbital Lift</t>
+          <t>Thang Nâng Quỹ Đạo</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Transport Vehicle</t>
+          <t>Phương Tiện Vận Chuyển</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Unique Settlement</t>
+          <t>Khu Định Cư Đặc Biệt</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Alarm Bird</t>
+          <t>Chim Cảnh Báo</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Bóng Ma Khổng Lồ Tại Lãnh Nguyên</t>
+          <t>Bóng Đen Khổng Lồ Trên Vùng Đất Băng Giá</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tìm kiếm nào! Những mảnh vụn của Lahai-Roi</t>
+          <t>Tìm kiếm! Mảnh vỡ Lahai-Roi</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Namipon Lightbox</t>
+          <t>Đèn hộp Namipon</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Namipon Telephone Booth</t>
+          <t>Buồng điện thoại Namipon</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Namipon Lightbox</t>
+          <t>Đèn hộp Namipon</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Namipon Capsule Machine</t>
+          <t>Máy Bán Hộp Ngẫu Nhiên Namipon</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Irideglow Portal</t>
+          <t>Cổng Irideglow</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Lament Residue Zone</t>
+          <t>Khu Vực Dư Lượng Âm Than</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Unusual Discord</t>
+          <t>Tacet Discord Kỳ Lạ</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Sticker Effects</t>
+          <t>Hiệu ứng Sticker</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mở khóa ô điều kiện tiên quyết trước</t>
+          <t>Hãy mở khóa ô điều kiện trước</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Đang Tiến Hành</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Post-Doomsday Coffee</t>
+          <t>Cà Phê Hậu Tận Thế</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 1.200.000 Bánh Dango Gạo để mở khóa Avatar "Cà Phê Hậu Tận Thế"</t>
+          <t>Thu thập tổng cộng 1.200.000 Bánh Gạo Dango để mở khóa Avatar "Cà Phê Hậu Tận Thế"</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Lament Residue Intensity</t>
+          <t>Cường Độ Dư Lượng Âm Than</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Không có vật phẩm để bán</t>
+          <t>Không có vật phẩm nào để bán</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Thường</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Hiếm</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Độc nhất</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Limited</t>
+          <t>Giới hạn</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Huyền Thoại</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Ổn Định</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Sắp xếp hoàn tất</t>
+          <t>Đã phân loại xong</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Sakura Quarter</t>
+          <t>Khu Sakura</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Meishin Passageway</t>
+          <t>Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Honami City</t>
+          <t>Thành Phố Honami</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Honami City</t>
+          <t>Thành Phố Honami</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Neon Tower</t>
+          <t>Tháp Neon</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Hồ Sơ Vụ Án Namipon</t>
+          <t>Hồ Sơ Bí Mật Namipon</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Honami City Lineup Editing</t>
+          <t>Chỉnh đội hình Thành phố Honami</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Đi đến bản đồ bên phải rồi nhấn lại để tiếp tục</t>
+          <t>Đến bản đồ bên phải rồi nhấn tiếp để tiến hành</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi trong Chế độ Hợp tác</t>
+          <t>Không thể chuyển đổi trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Đường Cao Tốc Observatory-Academy</t>
+          <t>Đường Cao Tốc Đài Quan Sát - Học Viện</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Orbit Valley Pass - Bắc</t>
+          <t>Đèo Thung Lũng Quỹ Đạo - Phía Bắc</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Orbit Valley Pass - Nam</t>
+          <t>Đèo Thung Lũng Quỹ Đạo - Phía Nam</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Sandreach Passage</t>
+          <t>Hành Lang Cát Vàng</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Farer's Road</t>
+          <t>Con Đường Người Đi Xa</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Sol's Embrace</t>
+          <t>Ôm Ấp Của Sol</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đỉnh Nhảy Sao</t>
+          <t>Vút Bay Ngôi Sao</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đường hầm Gió Hú</t>
+          <t>Đường Hầm Gào Thét</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Cầu Spacetrek-Bjartr</t>
+          <t>Cầu Spacetrek–Bjartr</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đường hầm Ngập Nước</t>
+          <t>Đường Hầm Ngập Nước</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Tiếp tục xây dựng lại mạng lưới tuyến và nâng Hoạt động Mạng lên 600 điểm</t>
+          <t>Tiếp tục khôi phục mạng lưới tuyến đường và nâng Hoạt Động Mạng lên 600 điểm</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Tiếp tục xây dựng lại mạng lưới tuyến và nâng Hoạt động Mạng lên 1.200 điểm</t>
+          <t>Tiếp tục khôi phục mạng lưới tuyến đường và nâng Hoạt Động Mạng lên 1.200 điểm</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Tiếp tục xây dựng lại mạng lưới tuyến và nâng Hoạt động Mạng lên 2.100 điểm</t>
+          <t>Tiếp tục khôi phục mạng lưới tuyến đường và nâng Hoạt Động Mạng lên 2.100 điểm</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Giai đoạn I: Nền tảng</t>
+          <t>Giai đoạn I: Nền Móng</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Giai đoạn II: Nền tảng</t>
+          <t>Giai đoạn II: Bệ Phóng</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Giai đoạn III: Giám sát</t>
+          <t>Giai đoạn III: Vọng Gác</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory</t>
+          <t>Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Tôi...</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Thông điệp Cảm ơn</t>
+          <t>Lời Cảm Ơn</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Mạng lưới Đang Hoạt động</t>
+          <t>Đang kết nối mạng</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Route Status</t>
+          <t>Trạng Thái Tuyến Đường</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Đang chờ</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Giai đoạn Hiện tại</t>
+          <t>Giai Đoạn Hiện Tại</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Tiến độ Giai đoạn</t>
+          <t>Tiến Độ Giai Đoạn</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Tuyến đường có thể được xây dựng lại ngay bây giờ</t>
+          <t>Giờ đây, tuyến đường có thể được xây dựng lại rồi.</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Giai đoạn hiện tại có thể bắt đầu ngay bây giờ</t>
+          <t>Giai đoạn hiện tại có thể bắt đầu ngay bây giờ.</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Rebuild Complete</t>
+          <t>Hoàn Thành Tái Xây Dựng</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Thời Gian Xây Dựng Lại</t>
+          <t>Thời gian tái thiết</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Unmark</t>
+          <t>Bỏ đánh dấu</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory Files</t>
+          <t>Hồ Sơ Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Các Thông điệp Cảm ơn</t>
+          <t>Những Lời Tri Ân</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Nhận thưởng</t>
+          <t>Nhận</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Giai đoạn Nền tảng</t>
+          <t>Giai Đoạn Cơ Bản</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Giai đoạn Nền tảng</t>
+          <t>Giai Đoạn Nền Tảng</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Unmark</t>
+          <t>Bỏ đánh dấu</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sinh viên Đại học Rabelle</t>
+          <t>Học sinh Đại học Rabelle</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu của Spacetrek Collective</t>
+          <t>Nhà nghiên cứu thuộc Tập thể Spacetrek</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ hướng dẫn "Chiến dịch: Phục hưng Biên giới"</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Chiến Dịch: Phục Hưng Biên Giới"</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đến Học viện trong Nhiệm vụ chính "Điều thiêu đốt dưới vùng đất băng giá"</t>
+          <t>Hoàn thành nhiệm vụ chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên" và đến Học Viện</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Unlocks Function</t>
+          <t>Mở khóa Chức năng</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Transmit Signal</t>
+          <t>Truyền Tín Hiệu</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Hoàn thành xây dựng lại Đài thiên văn Spacetrek để mở khóa</t>
+          <t>Xây dựng lại hoàn toàn Đài Thiên văn Spacetrek để mở khóa</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Vui lòng tiếp tục xây dựng lại Đài thiên văn Spacetrek</t>
+          <t>Hãy tiếp tục tái thiết Đài Thiên Văn Spacetrek.</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tìm Soliskin bị mất tích</t>
+          <t>Tìm một mảnh Soliskin thất lạc</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Đạt đến Giai đoạn nền tảng trong việc xây dựng lại Đài thiên văn Spacetrek</t>
+          <t>Hoàn thành Giai đoạn Cơ bản trong việc tái thiết Đài thiên văn Spacetrek</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Khám phá tại Giant's Gaze</t>
+          <t>Khám phá 40% Tầm Nhìn Khổng Lồ</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Đến Học viện Startorch</t>
+          <t>Đến Học Viện Startorch</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Hoàn thành một trận đấu trong "Đỉnh cao Danh vọng: Trận đấu Tái sinh"</t>
+          <t>Hoàn thành một trận đấu trong "Đỉnh Danh Vọng: Trận Tái Đấu"</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ "Khoảnh khắc Ghi lại trong Ánh sáng"</t>
+          <t>Hoàn thành Nhiệm Vụ "Khoảnh Khắc Ánh Sáng Ghi Dấu"</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Khám phá tại Học viện Startorch</t>
+          <t>Đạt 40% Tiến Độ Thám Hiểm tại Học Viện Startorch</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Đi Starward Riseway đến Viện Nghiên cứu</t>
+          <t>Đến Viện Nghiên Cứu qua Starward Riseway</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Khám phá tại Starward Riseway</t>
+          <t>Đạt 40% Tiến Độ Thám Hiểm tại Con Đường Ngôi Sao</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Geospider S4 để loại bỏ Lumiglow Shade một lần</t>
+          <t>Dùng Máy Chiếu: Geospider S4 loại bỏ Bóng Lumin một lần</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Lưu trữ một Vista View</t>
+          <t>Lưu trữ một cảnh quan Vista View</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Đánh bại Voidworm</t>
+          <t>Tiêu diệt Voidworm</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Thám hiểm ở Mawburrow Desert</t>
+          <t>Khám phá 40% Sa Mạc Mawburrow</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Sử dụng Route Constructor một lần</t>
+          <t>Sử dụng Bộ Xây Dựng Lộ Trình một lần</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Hoàn thành một Thử thách Điểm Kho báu</t>
+          <t>Hoàn thành Thử Thách Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Zip Zap để chiếu sáng một petroglyph</t>
+          <t>Sử dụng Máy Chiếu: Zip Zap chiếu sáng một bức tranh khắc đá</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Thám hiểm ở Etching Plains</t>
+          <t>Khám phá 40% Đồng Bằng Etching</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Dọn dẹp một Void Storm Zone một lần</t>
+          <t>Dọn sạch một Khu Bão Hư Không một lần</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hoàn thành Ngắm sao Suối nước nóng một lần</t>
+          <t>Hoàn thành Ngắm Sao Suối Nước Nóng 1 lần</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Hoàn thành hướng dẫn lái xe</t>
+          <t>Hoàn thành hướng dẫn lái phương tiện</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Thám hiểm ở Rebirth Uplands</t>
+          <t>Khám phá 40% Cao Nguyên Tái Sinh</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Dọn dẹp một Tacet Discord Nest một lần</t>
+          <t>Tiêu diệt một Tổ Tacet Discord một lần</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Thám hiểm "Giai điệu thất lạc"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Giai Điệu Lạc Lõng".</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Phụ "Mechascout vô song"</t>
+          <t>Hoàn thành nhiệm vụ phụ "Thợ Máy Trinh Sát Vô Địch"</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Thám hiểm ở Stagnant Run</t>
+          <t>Đạt 40% Tiến Độ Thám Hiểm tại Dòng Chảy Tắc Nghẽn</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Zip Zap để khởi động lại một Spacetrek Explorer một lần</t>
+          <t>Dùng Máy Chiếu: Zip Zap khởi động lại Spacetrek Explorer một lần</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Phụ "Bắt gió"</t>
+          <t>Hoàn thành nhiệm vụ phụ "Bắt Gió"</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Hoàn thành Khởi động lại Smartprint Cube một lần</t>
+          <t>Khởi động lại Khối Smartprint một lần</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Thám hiểm ở Fangspire Chasm</t>
+          <t>Khám phá 40% Hẻm Núi Fangspire</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Mining Reindeer để giải cứu một Soliskin bị mắc kẹt trong Luxite</t>
+          <t>Sử dụng Máy Chiếu: Mining Reindeer giải cứu Soliskin bị mắc kẹt trong Luxite</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Thám hiểm "Nơi ánh sáng định hình"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Nơi Ánh Sáng Hóa Hình".</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Đạt 40% Tiến độ Thám hiểm ở Bjartr Woods</t>
+          <t>Khám phá 40% Bjartr Woods</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Thử thách đua Route Constructor I</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường I</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Thử thách đua Route Constructor II</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường II</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường XII</t>
+          <t>Giải Đua Xây Dựng Tuyến Đường XII</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Đạt Điểm B</t>
+          <t>Đạt điểm B</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Đạt Điểm A</t>
+          <t>Đạt điểm A</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Đạt Điểm S</t>
+          <t>Đạt điểm S</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận giấy phép xe máy thám hiểm</t>
+          <t>Mở khóa sau khi nhận giấy phép xe máy thám hiểm.</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Xây dựng lại Farer's Road để mở khóa</t>
+          <t>Mở khóa Con Đường Người Lang Thang bằng cách tái thiết</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Nơi Ánh Sáng Hình Thành" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Nơi Ánh Sáng Hóa Hình" để mở khóa</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Exploration Data</t>
+          <t>Dữ Liệu Thám Hiểm</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>MAX</t>
+          <t>TỐI ĐA</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Đến Học Viện trong Nhiệm Vụ Chính "Điều Gì Cháy Bên Dưới Vùng Đất Băng Giá"</t>
+          <t>Hoàn thành nhiệm vụ chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên" và đến Học Viện</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Insufficient Exploration Data</t>
+          <t>Dữ liệu Thám Hiểm không đủ</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Vui lòng đạt cấp độ tiên quyết</t>
+          <t>Hãy đạt đến cấp độ yêu cầu trước.</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Nâng cấp Available</t>
+          <t>Có thể nâng cấp</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Nhận Nhiệm Vụ Sự Kiện "Đỉnh Cao Uy Tín: Trận Đấu Tái Diễn" tại Học Viện Startorch</t>
+          <t>Nhận Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Diễn" tại Học Viện Startorch</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Nhận nhiệm vụ "Những Khoảnh Khắc Được Ghi Lại Trong Ánh Sáng" tại Học Viện Startorch</t>
+          <t>Nhận nhiệm vụ "Khoảnh Khắc Ánh Sáng Ghi Dấu" tại Học Viện Startorch</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Nhận nhiệm vụ "Biển Cả Trong Tầm Tay" sau khi xây dựng lại Submerged Tunnel</t>
+          <t>Nhận nhiệm vụ "Biển Cả Trong Tầm Tay" sau khi khôi phục Đường Hầm Ngập Nước</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Chiến Dịch: Đổi Mới Biên Giới"</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Chiến Dịch: Tái Sinh Biên Giới"</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận giấy phép xe máy thám hiểm</t>
+          <t>Mở khóa sau khi nhận giấy phép xe máy thám hiểm.</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Nhận nhiệm vụ "Giai Điệu Bị Lãng Quên" tại Jetrified Ridge ở Stagnant Run</t>
+          <t>Nhận nhiệm vụ "Giai Điệu Lạc Mất" tại Jetrified Ridge, Stagnant Run</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Nhận nhiệm vụ "Unparalleled Mechascout" sau khi xây dựng lại Sol's Embrace</t>
+          <t>Nhận nhiệm vụ "Kẻ Trinh Sát Cơ Giới Vô Đối" sau khi khôi phục Sol's Embrace</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Nhận nhiệm vụ "Catch the Wind" sau khi xây dựng lại Sol's Embrace</t>
+          <t>Nhận nhiệm vụ "Bắt Gió" sau khi tái thiết Sol's Embrace</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Nhận Nhiệm Vụ Thám Hiểm "Where Light Takes Shape" tại Bjartr Woods</t>
+          <t>Nhận Nhiệm Vụ Thám Hiểm "Nơi Ánh Sáng Hóa Hình" tại Bjartr Woods</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Projector: Geospider S4</t>
+          <t>Bộ chiếu: Geospider S4</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Vista View</t>
+          <t>Góc Nhìn Bao Quát</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Projector: Zip Zap</t>
+          <t>Máy chiếu: Zip Zap</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Projector: Mining Reindeer</t>
+          <t>Máy chiếu: Mining Reindeer</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Geospider S4 để loại bỏ Lumiglow Shade</t>
+          <t>Dùng Máy Chiếu: Geospider S4 để loại bỏ Bóng Lumin</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Lưu một Vista View vào Archive</t>
+          <t>Lưu trữ một cảnh quan Vista View</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Zip Zap để khởi động lại một Spacetrek Explorer một lần</t>
+          <t>Dùng Máy Chiếu: Zip Zap khởi động lại Spacetrek Explorer một lần</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Sử dụng Projector: Mining Reindeer để giải cứu một Soliskin bị mắc kẹt trong Luxite</t>
+          <t>Sử dụng Máy Chiếu: Mining Reindeer giải cứu Soliskin bị mắc kẹt trong Luxite</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Hoàn thành Hướng Dẫn Nhiệm Vụ "Operation: Frontier Renewal" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Chiến Dịch: Phục Hưng Biên Giới" để mở khóa</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Insufficient Network Activity</t>
+          <t>Hoạt Động Mạng không đủ.</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục Nhiệm Vụ Thám Hiểm "Operation: Frontier Renewal"</t>
+          <t>Hãy tiếp tục Nhiệm Vụ Thám Hiểm "Chiến Dịch: Tái Thiết Biên Cương"</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Hãy tiếp tục Nhiệm Vụ Thám Hiểm Operation: Frontier Renewal</t>
+          <t>Hãy tiếp tục Nhiệm Vụ Thám Hiểm Chiến Dịch: Tái Thiết Biên Cương</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Độ Khó</t>
+          <t>Độ khó</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Cloudy</t>
+          <t>U Ám</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Rainy</t>
+          <t>Mưa</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Misty</t>
+          <t>Sương Mù</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Ethereal Starveil</t>
+          <t>Màn Sương Sao Hư Ảo</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Meteor Shower</t>
+          <t>Mưa Sao Băng</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Prismatic Glow</t>
+          <t>Ánh Sáng Sắc Cầu</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Spacetrek Collective</t>
+          <t>Tập Đoàn Spacetrek</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Black Tea</t>
+          <t>Trà Đen</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Iced Tea</t>
+          <t>Trà Đá</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Sunflare Nectar</t>
+          <t>Mật Hoa Ánh Dương</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Olive Juice</t>
+          <t>Nước Ép Ô Liu</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bitter Melon Juice</t>
+          <t>Nước Khổ Qua</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Plant Milk</t>
+          <t>Sữa Thực Vật</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Lemon Juice</t>
+          <t>Nước Chanh Tươi</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Viscum Berry Bits</t>
+          <t>Mảnh Quả Tầm Gửi</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Crushed Nuts</t>
+          <t>Hạt nghiền</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Red Pearls</t>
+          <t>Ngọc Trai Đỏ</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Lemon Peel</t>
+          <t>Vỏ Chanh</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Dried Berries</t>
+          <t>Quả Mọng Khô</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Sour Plum Cubes</t>
+          <t>Khối Mận Chua</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Orange Slice</t>
+          <t>Múi Cam</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Lemongrass</t>
+          <t>Sả Dại</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Laurus Leaf</t>
+          <t>Lá Laurus</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Two-Tone Marshmallow</t>
+          <t>Kẹo Dẻo Hai Màu</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Crushed Cookies</t>
+          <t>Bánh quy nghiền</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Star Fruit</t>
+          <t>Trái Sao</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Duet of Teas</t>
+          <t>Trà Đôi</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nectar Black Tea</t>
+          <t>Trà Đen Mật Hoa</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Olive Black Tea</t>
+          <t>Trà Ô Liu Đen</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Coffee with Tea</t>
+          <t>Cà phê Trà</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Vitality Black Tea</t>
+          <t>Trà Đen Tăng Sinh Lực</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Plant Milk Tea</t>
+          <t>Trà Sữa Thực Vật</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Lemon Black Tea</t>
+          <t>Trà Chanh Đen</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Nectar Iced Tea</t>
+          <t>Trà Đá Mật Hoa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Olive Iced Tea</t>
+          <t>Trà Đá Ô Liu</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Matcha Coffee</t>
+          <t>Cà phê Matcha</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Vitality Iced Tea</t>
+          <t>Trà Năng Lượng Đá</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Plant Milk Green Tea</t>
+          <t>Trà Xanh Sữa Thực Vật</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Lemon Iced Tea</t>
+          <t>Trà Chanh Đá</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Olive Nectar</t>
+          <t>Mật Hoa Ô Liu</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Sunflare Signature Coffee</t>
+          <t>Cà Phê Đặc Biệt Ánh Dương</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Bitter Melon Nectar</t>
+          <t>Mật Khổ Qua</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nectar Milk</t>
+          <t>Sữa Mật Hoa</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Sunflare Lemonade</t>
+          <t>Nước Chanh Ánh Dương</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Olive Coffee</t>
+          <t>Cà Phê Ô Liu</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Bitter Melon Olive Juice</t>
+          <t>Nước Khổ Qua Ô Liu</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Olive Milk</t>
+          <t>Sữa Ô Liu</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Olive Lemonade</t>
+          <t>Nước Chanh Ô Liu</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Bitter Melon Coffee</t>
+          <t>Cà Phê Khổ Qua</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Frostland Latte</t>
+          <t>Cà Phê Latte Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Lemon Coffee</t>
+          <t>Cà Phê Chanh</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Bitter Melon Milk</t>
+          <t>Sữa Khổ Qua</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Bitter Melon Lemonade</t>
+          <t>Nước Chanh Khổ Qua</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Lemon Milk</t>
+          <t>Sữa Chanh</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Bổ Sung Black Tea</t>
+          <t>Trà Đen Phụ</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Bổ Sung Iced Tea</t>
+          <t>Trà Đá Phụ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Concentrated Sunflare Nectar</t>
+          <t>Mật Hoa Nắng Cô Đặc</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Concentrated Olive Juice</t>
+          <t>Nước Ô Liu Cô Đặc</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Double Espresso</t>
+          <t>Espresso Kép</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Concentrated Bitter Melon Juice</t>
+          <t>Nước Mướp Đắng Cô Đặc</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Concentrated Plant Milk</t>
+          <t>Sữa Thực Vật Cô Đặc</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Concentrated Lemon Juice</t>
+          <t>Nước Chanh Cô Đặc</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Not Satisfied</t>
+          <t>Chưa đạt yêu cầu</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Tàm tạm</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Hài lòng</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Rất Hài Lòng</t>
+          <t>Hài lòng lắm.</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Olive Iced Tea</t>
+          <t>Trà Đá Ô Liu</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Nectar Black Tea</t>
+          <t>Trà Đen Mật Hoa</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Frostland Latte</t>
+          <t>Cà Phê Latte Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Drink Orders</t>
+          <t>Đơn Đặt Đồ Uống</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Drink Flavor</t>
+          <t>Hương Vị Đồ Uống</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Chọn Nước Uống Cơ Bản</t>
+          <t>Chọn Nguyên Liệu Đồ Uống</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Tiếp Theo</t>
+          <t>Tiếp theo</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Finish</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Ánh Sáng</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Trung bình</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Bổ Sung</t>
+          <t>Phụ</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Sử dụng Olive Juice</t>
+          <t>Dùng Olive Juice</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Sử dụng Viscum Berry Bits</t>
+          <t>Dùng Viscum Berry Bits.</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Sử dụng Lemongrass</t>
+          <t>Sử dụng Cỏ Chanh</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Sử dụng Viscum Berry Bits</t>
+          <t>Dùng Viscum Berry Bits.</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Quả mọng nhỏ màu đỏ</t>
+          <t>Quả mọng đỏ nhỏ</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cam tươi thái lát</t>
+          <t>Cam mới bổ</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Bánh quy nghiền vụn</t>
+          <t>Bánh quy vụn</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
